--- a/DB Design.xlsx
+++ b/DB Design.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nazeer Joseph Data Universe\Data Load\Netsuite ETL Full Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04F9741E-B0CC-4606-A827-1D344A8B80F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A24A4058-B962-4671-A0EA-AFA922AA2E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{008B9030-4E5F-4F51-8597-5711FEDEC6CF}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Schema" sheetId="1" r:id="rId1"/>
     <sheet name="DBML" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Schema!$A$1:$B$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
